--- a/Data/xlxs/smartwatch_cleaned_statistics_fixed.xlsx
+++ b/Data/xlxs/smartwatch_cleaned_statistics_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Smart-Watch-Stats-Project\Data\xlxs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961A599E-31B7-4E1F-8A55-27919202F55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2006AF5-59D5-4E3E-A4CA-B5C16CCD9FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statistics" sheetId="1" r:id="rId1"/>
@@ -519,7 +519,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,6 +529,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6161"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,80 +551,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="53">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -997,8 +952,67 @@
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6161"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1011,7 +1025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{608EBCD2-6D24-4D23-891F-9723046FD8E9}" name="Table1" displayName="Table1" ref="B4:X35" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{608EBCD2-6D24-4D23-891F-9723046FD8E9}" name="Table1" displayName="Table1" ref="B4:X35" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="B4:X35" xr:uid="{608EBCD2-6D24-4D23-891F-9723046FD8E9}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{67458E5E-E663-4533-8FC4-1D9546780BBC}" name="Group Type"/>
@@ -1020,207 +1034,207 @@
     <tableColumn id="4" xr3:uid="{6CD379F3-D2D6-4BD2-B64A-92F429F1E655}" name="Model"/>
     <tableColumn id="5" xr3:uid="{3C2EB0A8-0BAD-4378-89F0-5BDD9153042B}" name="Platform"/>
     <tableColumn id="6" xr3:uid="{6CE3D0B5-1BD4-48B8-B479-E6E34C13ABDB}" name="n"/>
-    <tableColumn id="7" xr3:uid="{B132AE66-45FF-404C-8FE1-225BFA1B609B}" name="Price Mean" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{D93DD236-57DE-4C10-9C84-D6BFBB0CF138}" name="Price Median" dataDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{441B8F93-59E0-44CB-975D-F74259024454}" name="Price SD" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{B596794B-3611-4E3E-8C66-54408D9A271E}" name="Price CV (%)" dataDxfId="49">
+    <tableColumn id="7" xr3:uid="{B132AE66-45FF-404C-8FE1-225BFA1B609B}" name="Price Mean" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{D93DD236-57DE-4C10-9C84-D6BFBB0CF138}" name="Price Median" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{441B8F93-59E0-44CB-975D-F74259024454}" name="Price SD" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{B596794B-3611-4E3E-8C66-54408D9A271E}" name="Price CV (%)" dataDxfId="45">
       <calculatedColumnFormula>IF(OR(G5&lt;2,H5=0),"",J5/H5*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{921DAC6C-48BB-427A-BCA1-B2F7243D1D39}" name="Price Min" dataDxfId="48"/>
-    <tableColumn id="12" xr3:uid="{62608AB5-9B27-4290-8269-58077B61222B}" name="Price Q1" dataDxfId="47"/>
-    <tableColumn id="13" xr3:uid="{2F9FDB44-93F4-438D-8D00-00ED156DAD26}" name="Price Q3" dataDxfId="46"/>
-    <tableColumn id="14" xr3:uid="{5244D297-7371-414A-A1CC-DFA9E941ABE8}" name="Price Max" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{921DAC6C-48BB-427A-BCA1-B2F7243D1D39}" name="Price Min" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{62608AB5-9B27-4290-8269-58077B61222B}" name="Price Q1" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{2F9FDB44-93F4-438D-8D00-00ED156DAD26}" name="Price Q3" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{5244D297-7371-414A-A1CC-DFA9E941ABE8}" name="Price Max" dataDxfId="41"/>
     <tableColumn id="15" xr3:uid="{3762D7F6-B63A-460C-8353-ED41BCD0B4AA}" name="Rating n"/>
-    <tableColumn id="16" xr3:uid="{DB1AA01E-EA6E-4CB1-B45C-8515EB6EA389}" name="Rating Mean" dataDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{0C4BB8AE-B734-4655-994E-6D3AD5A32FF6}" name="Rating Median" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{723CB2AA-8C24-4054-9C00-5288D705A4F7}" name="Rating SD" dataDxfId="42"/>
-    <tableColumn id="19" xr3:uid="{64A1CFDD-7A08-49D7-88C1-32B0F5C32D77}" name="Rating CV (%)" dataDxfId="41">
+    <tableColumn id="16" xr3:uid="{DB1AA01E-EA6E-4CB1-B45C-8515EB6EA389}" name="Rating Mean" dataDxfId="40"/>
+    <tableColumn id="17" xr3:uid="{0C4BB8AE-B734-4655-994E-6D3AD5A32FF6}" name="Rating Median" dataDxfId="39"/>
+    <tableColumn id="18" xr3:uid="{723CB2AA-8C24-4054-9C00-5288D705A4F7}" name="Rating SD" dataDxfId="38"/>
+    <tableColumn id="19" xr3:uid="{64A1CFDD-7A08-49D7-88C1-32B0F5C32D77}" name="Rating CV (%)" dataDxfId="37">
       <calculatedColumnFormula>IF(OR(P5&lt;2,Q5=0),"",S5/Q5*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{19D7E071-1F24-4354-8655-D9889530DBA4}" name="Rating Min" dataDxfId="40"/>
-    <tableColumn id="21" xr3:uid="{C5278980-1389-465D-8C80-305B1ADD8D6D}" name="Rating Q1" dataDxfId="39"/>
-    <tableColumn id="22" xr3:uid="{BACFD2F4-8FD5-490E-8D52-8D4B7EA7B9D4}" name="Rating Q3" dataDxfId="38"/>
-    <tableColumn id="23" xr3:uid="{2E494D6A-E1BF-4418-B7A2-2A52C4EDF368}" name="Rating Max" dataDxfId="37"/>
+    <tableColumn id="20" xr3:uid="{19D7E071-1F24-4354-8655-D9889530DBA4}" name="Rating Min" dataDxfId="36"/>
+    <tableColumn id="21" xr3:uid="{C5278980-1389-465D-8C80-305B1ADD8D6D}" name="Rating Q1" dataDxfId="35"/>
+    <tableColumn id="22" xr3:uid="{BACFD2F4-8FD5-490E-8D52-8D4B7EA7B9D4}" name="Rating Q3" dataDxfId="34"/>
+    <tableColumn id="23" xr3:uid="{2E494D6A-E1BF-4418-B7A2-2A52C4EDF368}" name="Rating Max" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F2DFCB97-D8F8-46BD-9201-82BFE252AFB8}" name="Table10" displayName="Table10" ref="B2:G40" totalsRowShown="0" headerRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F2DFCB97-D8F8-46BD-9201-82BFE252AFB8}" name="Table10" displayName="Table10" ref="B2:G40" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="B2:G40" xr:uid="{F2DFCB97-D8F8-46BD-9201-82BFE252AFB8}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E40D0A5C-6A8E-4EEC-969B-40176608B52E}" name="brand"/>
     <tableColumn id="2" xr3:uid="{10E2567F-55BA-485A-BA52-B29BE75DD946}" name="model"/>
     <tableColumn id="3" xr3:uid="{3D2449CB-8CD3-42DA-8BDC-9148F035C97C}" name="platform"/>
     <tableColumn id="4" xr3:uid="{3B6E882F-295D-45ED-AFA1-B824F78BE80F}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{CDFCC678-2A55-44F4-98F4-A752F86C80D0}" name="price" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{7B967933-54E0-4197-90BA-02740003D24B}" name="rating" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{CDFCC678-2A55-44F4-98F4-A752F86C80D0}" name="price" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{7B967933-54E0-4197-90BA-02740003D24B}" name="rating" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4085B424-BC45-4516-8F2F-4E61723E45DE}" name="Table11" displayName="Table11" ref="B2:G7" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{4085B424-BC45-4516-8F2F-4E61723E45DE}" name="Table11" displayName="Table11" ref="B2:G7" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="B2:G7" xr:uid="{4085B424-BC45-4516-8F2F-4E61723E45DE}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C60C316F-A75B-4420-9ECC-E7C683652E91}" name="brand"/>
     <tableColumn id="2" xr3:uid="{5D4F5CB5-9DC3-4602-B4DB-1125B37285D0}" name="model"/>
     <tableColumn id="3" xr3:uid="{F1F0F6DE-CE00-4E98-A439-9B55F6E79862}" name="platform"/>
     <tableColumn id="4" xr3:uid="{F98793CD-7209-46DE-930B-B43262054838}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{4D93B0CC-256E-4D8A-BA81-7E3B0F8C15C1}" name="price" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{0DAF1CB5-4E55-463C-8037-08CCB4AC1784}" name="rating" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{4D93B0CC-256E-4D8A-BA81-7E3B0F8C15C1}" name="price" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{0DAF1CB5-4E55-463C-8037-08CCB4AC1784}" name="rating" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{07647B4B-ADAE-49B9-AF20-04A3CBEF2A76}" name="Table14" displayName="Table14" ref="B2:G34" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{07647B4B-ADAE-49B9-AF20-04A3CBEF2A76}" name="Table14" displayName="Table14" ref="B2:G34" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="B2:G34" xr:uid="{07647B4B-ADAE-49B9-AF20-04A3CBEF2A76}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{8B794683-A45B-4580-9EAD-045CF9C202DC}" name="brand"/>
     <tableColumn id="2" xr3:uid="{4BBC79DA-8E64-4567-B20A-B3DF43B32D13}" name="model"/>
     <tableColumn id="3" xr3:uid="{326654EC-E67E-45EB-BD57-E2FE816B68E9}" name="platform"/>
     <tableColumn id="4" xr3:uid="{F42F692D-69A1-47E7-89F9-8ABB126650BA}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{BA2A5026-0272-4166-B014-7F57A6AEFED8}" name="price" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{166B9DDB-9C0D-4B4D-BC05-A43C3EBE75C7}" name="rating" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{BA2A5026-0272-4166-B014-7F57A6AEFED8}" name="price" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{166B9DDB-9C0D-4B4D-BC05-A43C3EBE75C7}" name="rating" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{4C678202-38FD-41AD-90C7-8928EB3E9BF6}" name="Table15" displayName="Table15" ref="B2:G6" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{4C678202-38FD-41AD-90C7-8928EB3E9BF6}" name="Table15" displayName="Table15" ref="B2:G6" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="B2:G6" xr:uid="{4C678202-38FD-41AD-90C7-8928EB3E9BF6}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{1E1486B1-02ED-4606-9EA8-7E68501FDDA7}" name="brand"/>
     <tableColumn id="2" xr3:uid="{75ADAE61-FA73-4B93-9A5E-7941AE69FED8}" name="model"/>
     <tableColumn id="3" xr3:uid="{31138AAC-B1AA-47D0-90E7-3B91532B1A05}" name="platform"/>
     <tableColumn id="4" xr3:uid="{BAA01264-E55F-47C4-A256-DC16057D8B7E}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{90C6BEE1-AE7F-4B31-B869-469AAA8A864A}" name="price" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{47918E95-14BB-4227-BB91-8460B27753A2}" name="rating" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{90C6BEE1-AE7F-4B31-B869-469AAA8A864A}" name="price" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{47918E95-14BB-4227-BB91-8460B27753A2}" name="rating" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{906FAACC-6CC3-4061-9964-52F041EEB448}" name="Table2" displayName="Table2" ref="B2:G117" totalsRowShown="0" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{906FAACC-6CC3-4061-9964-52F041EEB448}" name="Table2" displayName="Table2" ref="B2:G117" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="B2:G117" xr:uid="{906FAACC-6CC3-4061-9964-52F041EEB448}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{5F8A3743-7B2E-450F-8C88-897EE84D837A}" name="brand"/>
     <tableColumn id="2" xr3:uid="{E9E857EC-966F-4293-8B8A-5A770CB622B7}" name="model"/>
     <tableColumn id="3" xr3:uid="{7F139F35-B4F0-4FA0-B960-045DAD70040D}" name="platform"/>
     <tableColumn id="4" xr3:uid="{721E18BA-7F9E-45A5-8223-92E98854FFC7}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{1D020644-3DBB-439F-9F33-A85C0882378F}" name="price" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{7468242B-F6C3-45B0-B30A-2CC8AF8E0FB5}" name="rating" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{1D020644-3DBB-439F-9F33-A85C0882378F}" name="price" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{7468242B-F6C3-45B0-B30A-2CC8AF8E0FB5}" name="rating" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D9753A4-423D-4318-A8C3-AB998B29A260}" name="Table3" displayName="Table3" ref="B2:G6" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D9753A4-423D-4318-A8C3-AB998B29A260}" name="Table3" displayName="Table3" ref="B2:G6" totalsRowShown="0" headerRowDxfId="29">
   <autoFilter ref="B2:G6" xr:uid="{7D9753A4-423D-4318-A8C3-AB998B29A260}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C34BC1F2-B54A-4A22-8C98-E780A12D15DB}" name="brand"/>
     <tableColumn id="2" xr3:uid="{84E4E0EC-897E-4B5F-860C-AB13F8108009}" name="model"/>
     <tableColumn id="3" xr3:uid="{29AA954A-8E7B-478D-A771-15D909E50CA7}" name="platform"/>
     <tableColumn id="4" xr3:uid="{32935E93-46CC-46D5-8863-AD1083E94561}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{4D69F091-E8EF-4DDC-AC79-0008684A07BC}" name="price" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{4FD569B8-3944-4D43-A577-12318CBDEAC2}" name="rating" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{4D69F091-E8EF-4DDC-AC79-0008684A07BC}" name="price" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{4FD569B8-3944-4D43-A577-12318CBDEAC2}" name="rating" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A139ABC-D465-4B40-92B6-8C97957B8ED7}" name="Table4" displayName="Table4" ref="B2:G98" totalsRowShown="0" headerRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A139ABC-D465-4B40-92B6-8C97957B8ED7}" name="Table4" displayName="Table4" ref="B2:G98" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="B2:G98" xr:uid="{0A139ABC-D465-4B40-92B6-8C97957B8ED7}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{F238F6B0-2783-4D23-A079-8FAB1E2EB162}" name="brand"/>
     <tableColumn id="2" xr3:uid="{31BD49F0-A64F-4B64-BC15-2002A9BF9944}" name="model"/>
     <tableColumn id="3" xr3:uid="{C664571D-420E-4D1D-ADCC-A015E3ADB438}" name="platform"/>
     <tableColumn id="4" xr3:uid="{D9FB3E6A-2ACA-4AEB-8831-F5C94D7C8A0A}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{863E17D5-A9C0-4BDC-9F07-9E17EA0FD735}" name="price" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{48D10597-7F5D-4CAC-8FD8-C300DAD12618}" name="rating" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{863E17D5-A9C0-4BDC-9F07-9E17EA0FD735}" name="price" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{48D10597-7F5D-4CAC-8FD8-C300DAD12618}" name="rating" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EE051D89-69F4-42DD-B186-74AB34A74FF2}" name="Table5" displayName="Table5" ref="B2:G17" totalsRowShown="0" headerRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EE051D89-69F4-42DD-B186-74AB34A74FF2}" name="Table5" displayName="Table5" ref="B2:G17" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="B2:G17" xr:uid="{EE051D89-69F4-42DD-B186-74AB34A74FF2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6377EF2E-C1DF-47E0-B8D4-B1C236445154}" name="brand"/>
     <tableColumn id="2" xr3:uid="{0EAC1C41-D88C-4906-B0FF-492D4DF37727}" name="model"/>
     <tableColumn id="3" xr3:uid="{938BAF50-12CE-4F22-A1E2-4DCA71468076}" name="platform"/>
     <tableColumn id="4" xr3:uid="{5CD7E856-B247-4D29-9B78-4C53F4221A6C}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{1640B708-8860-4D77-ACD6-5DE65B04A3DF}" name="price" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{CC097140-F188-45A3-8526-139F6BEE4C08}" name="rating" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{1640B708-8860-4D77-ACD6-5DE65B04A3DF}" name="price" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{CC097140-F188-45A3-8526-139F6BEE4C08}" name="rating" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2C1BEE2F-536F-4904-BC76-10214916B6E9}" name="Table6" displayName="Table6" ref="B2:G3" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2C1BEE2F-536F-4904-BC76-10214916B6E9}" name="Table6" displayName="Table6" ref="B2:G3" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="B2:G3" xr:uid="{2C1BEE2F-536F-4904-BC76-10214916B6E9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{47E7C3BE-1277-4151-9943-930751221860}" name="brand"/>
     <tableColumn id="2" xr3:uid="{16CF62A7-45AB-4761-B3D6-FBB953C89456}" name="model"/>
     <tableColumn id="3" xr3:uid="{71205E56-427F-409C-AA48-858ED6DA3893}" name="platform"/>
     <tableColumn id="4" xr3:uid="{69BEFDB9-DB60-4D25-A625-3123F08E7159}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{8C64A8F3-34E9-4549-A9D3-448A40C43A73}" name="price" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{52FD0E9D-0378-4794-9838-54B7BE01E9FE}" name="rating" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{8C64A8F3-34E9-4549-A9D3-448A40C43A73}" name="price" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{52FD0E9D-0378-4794-9838-54B7BE01E9FE}" name="rating" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00DF2E08-75FE-42A6-A78B-7A0356719E91}" name="Table7" displayName="Table7" ref="B2:G28" totalsRowShown="0" headerRowDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00DF2E08-75FE-42A6-A78B-7A0356719E91}" name="Table7" displayName="Table7" ref="B2:G28" totalsRowShown="0" headerRowDxfId="17">
   <autoFilter ref="B2:G28" xr:uid="{00DF2E08-75FE-42A6-A78B-7A0356719E91}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{16864E9E-9C6C-4ADE-9371-CCBD0A603266}" name="brand"/>
     <tableColumn id="2" xr3:uid="{47FAABFD-38B8-4BD2-B6AC-EEBFB844BC2A}" name="model"/>
     <tableColumn id="3" xr3:uid="{C2613F48-F5E2-4737-B86D-3B00728DF669}" name="platform"/>
     <tableColumn id="4" xr3:uid="{16A57B03-E390-4426-A22F-1B6C6D567DC0}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{4DD9B738-E2D7-49DA-9C28-C1016312A6C0}" name="price" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{AE98BD57-7099-42B1-BD96-34598D9C8469}" name="rating" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{4DD9B738-E2D7-49DA-9C28-C1016312A6C0}" name="price" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{AE98BD57-7099-42B1-BD96-34598D9C8469}" name="rating" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39D7B939-1D12-4E20-89C1-D53803C035F2}" name="Table8" displayName="Table8" ref="B2:G8" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39D7B939-1D12-4E20-89C1-D53803C035F2}" name="Table8" displayName="Table8" ref="B2:G8" totalsRowShown="0" headerRowDxfId="52">
   <autoFilter ref="B2:G8" xr:uid="{39D7B939-1D12-4E20-89C1-D53803C035F2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0585998B-A599-4E85-9C6D-D0A5993AD135}" name="brand"/>
     <tableColumn id="2" xr3:uid="{04A956B8-C210-411F-998F-F5C9BB35471A}" name="model"/>
     <tableColumn id="3" xr3:uid="{07C204C7-3E42-421A-A34F-F48F61D4620D}" name="platform"/>
     <tableColumn id="4" xr3:uid="{E99DAA76-FA52-480C-A231-824B5F140354}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{42E6061D-6621-44D8-85A7-A6CF8AE8F06A}" name="price" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{0562D156-44BF-4498-BB6F-9C9C906DF822}" name="rating" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{42E6061D-6621-44D8-85A7-A6CF8AE8F06A}" name="price" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{0562D156-44BF-4498-BB6F-9C9C906DF822}" name="rating" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{230EFF72-2DCE-4FBC-BFD8-785775B3A380}" name="Table9" displayName="Table9" ref="B2:G5" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{230EFF72-2DCE-4FBC-BFD8-785775B3A380}" name="Table9" displayName="Table9" ref="B2:G5" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="B2:G5" xr:uid="{230EFF72-2DCE-4FBC-BFD8-785775B3A380}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{BAF19856-4A4D-41E6-BEEE-6BA4B4016F96}" name="brand"/>
     <tableColumn id="2" xr3:uid="{25F52879-9EED-4401-860D-30D1A6F8835D}" name="model"/>
     <tableColumn id="3" xr3:uid="{76B48441-0BB9-4FA0-A118-380DAB019639}" name="platform"/>
     <tableColumn id="4" xr3:uid="{EBE6F2EC-F0F2-4B1D-A94D-A407BD7F5251}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{5BABA774-C9DC-4BAA-896A-722EDFAA61E2}" name="price" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{CE6E7773-536C-440C-BC12-CF2EF47A6B21}" name="rating" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{5BABA774-C9DC-4BAA-896A-722EDFAA61E2}" name="price" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{CE6E7773-536C-440C-BC12-CF2EF47A6B21}" name="rating" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1444,127 +1458,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="17.399999999999999">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
     </row>
     <row r="2" spans="2:24" ht="14.4">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
     </row>
     <row r="4" spans="2:24" ht="24.6" customHeight="1">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="V4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="X4" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2402,42 +2416,43 @@
       </c>
     </row>
     <row r="15" spans="2:24">
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G15">
+      <c r="F15" s="8"/>
+      <c r="G15" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15">
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
     </row>
     <row r="16" spans="2:24">
       <c r="B16" t="s">
@@ -2701,45 +2716,45 @@
       </c>
     </row>
     <row r="19" spans="2:24">
-      <c r="B19" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19">
+      <c r="F19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19">
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
     </row>
     <row r="20" spans="2:24">
       <c r="B20" t="s">
@@ -2863,7 +2878,7 @@
         <v>5820.3130808380365</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" si="2"/>
+        <f>IF(OR(G21&lt;2,H21=0),"",J21/H21*100)</f>
         <v>76.510273677770613</v>
       </c>
       <c r="L21" s="1">
@@ -3632,86 +3647,86 @@
       </c>
     </row>
     <row r="30" spans="2:24">
-      <c r="B30" t="s">
+      <c r="B30" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F30" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30">
+      <c r="F30" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
     </row>
     <row r="31" spans="2:24">
-      <c r="B31" t="s">
+      <c r="B31" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F31" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31">
+      <c r="F31" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="8">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
     </row>
     <row r="32" spans="2:24">
       <c r="B32" t="s">
@@ -4094,22 +4109,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4866,22 +4881,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5004,22 +5019,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5041,22 +5056,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5697,22 +5712,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5813,22 +5828,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="38.4" customHeight="1">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8027,22 +8042,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8147,22 +8162,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10035,22 +10050,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10363,22 +10378,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10423,22 +10438,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10963,22 +10978,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -11117,22 +11132,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>49</v>
       </c>
     </row>

--- a/Data/xlxs/smartwatch_cleaned_statistics_fixed.xlsx
+++ b/Data/xlxs/smartwatch_cleaned_statistics_fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Smart-Watch-Stats-Project\Data\xlxs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2006AF5-59D5-4E3E-A4CA-B5C16CCD9FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A61CE95-B95C-4D13-A2FC-4A8B42766A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statistics" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,32 @@
     <sheet name="Galaxy_Ultra" sheetId="13" r:id="rId13"/>
     <sheet name="Huawei_Ultimate" sheetId="14" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">All_Data!$C$3:$C$117</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">All_Data!$C$3:$C$117</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">All_Data!$C$3:$C$117</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">All_Data!$C$3:$C$117</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">All_Data!$C$22:$C$117</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">All_Data!$F$22:$F$117</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">All_Data!$C$3:$C$117</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">All_Data!$F$2</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">All_Data!$F$3:$F$117</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">All_Data!$C$3:$C$117</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">All_Data!$F$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -561,19 +587,49 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="53">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -976,36 +1032,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1024,8 +1050,2792 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>All_Data!$F$3:$F$117</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="115"/>
+                <c:pt idx="0">
+                  <c:v>15900</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18130</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20900</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9990</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3990</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3990</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3990</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3690</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20980.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4990</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4990</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4080</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4990</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>23900</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14900</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19900</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19900</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>28990</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>17990</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>29950</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23390</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>22410</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>23350</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>23350</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>23769</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13980</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>14290</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15990</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>12980</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>14290</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>13890</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>18790</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26145</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>13790</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>14405</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>17880</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>17490</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>19175</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>14290</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>26399</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>19920</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>17067</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>13900</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>12990</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>32790</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>34055</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1047.45</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1045.21</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1159.17</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>826.39</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>579.21</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>10659</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7490</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5899</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4990</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>566.35</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>11618</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>7990</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>429</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>563</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7990</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6990</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1624</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>10659</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>9180</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>9286</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>20995</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>15619</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>11900</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>11819</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>13900</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>10990</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>12693</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>9999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>7790</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>12119</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>11900</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13090</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>13090</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5820</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5133</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5120</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>8130</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6417.87</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6849</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5990</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>12495</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7790</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>6980</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>10590</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>8490</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>8690</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>9999</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>16703</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>12619</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>15459</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>15927</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>16009</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>9520</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>10747</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>All_Data!$G$3:$G$117</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="115"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FF13-4745-8E19-11B337BC7BB0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="671880959"/>
+        <c:axId val="658918895"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="671880959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="658918895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="658918895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="671880959"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.18</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{00000000-7464-4750-9011-0154E337F6D6}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.17</cx:f>
+              <cx:v>price</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.14</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.16</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000000-A25C-47D2-B98A-23C73C8077A9}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.15</cx:f>
+              <cx:v>price</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>615537</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>495</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>376052</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>109849</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Chart 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A3CA549-6C37-5D09-9DF1-96C51E528FC2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10867901" y="845622"/>
+              <a:ext cx="6410696" cy="4431972"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>394853</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>110836</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>429491</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>96982</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65A497D3-CF51-A371-0C6A-BBD4F054A16B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533398</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>110836</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38B4D14E-C974-8ED1-549E-295E49ABF0C7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10805158" y="5902036"/>
+              <a:ext cx="10317482" cy="6960524"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{608EBCD2-6D24-4D23-891F-9723046FD8E9}" name="Table1" displayName="Table1" ref="B4:X35" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{608EBCD2-6D24-4D23-891F-9723046FD8E9}" name="Table1" displayName="Table1" ref="B4:X35" totalsRowShown="0" headerRowDxfId="52">
   <autoFilter ref="B4:X35" xr:uid="{608EBCD2-6D24-4D23-891F-9723046FD8E9}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{67458E5E-E663-4533-8FC4-1D9546780BBC}" name="Group Type"/>
@@ -1034,27 +3844,27 @@
     <tableColumn id="4" xr3:uid="{6CD379F3-D2D6-4BD2-B64A-92F429F1E655}" name="Model"/>
     <tableColumn id="5" xr3:uid="{3C2EB0A8-0BAD-4378-89F0-5BDD9153042B}" name="Platform"/>
     <tableColumn id="6" xr3:uid="{6CE3D0B5-1BD4-48B8-B479-E6E34C13ABDB}" name="n"/>
-    <tableColumn id="7" xr3:uid="{B132AE66-45FF-404C-8FE1-225BFA1B609B}" name="Price Mean" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{D93DD236-57DE-4C10-9C84-D6BFBB0CF138}" name="Price Median" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{441B8F93-59E0-44CB-975D-F74259024454}" name="Price SD" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{B596794B-3611-4E3E-8C66-54408D9A271E}" name="Price CV (%)" dataDxfId="45">
+    <tableColumn id="7" xr3:uid="{B132AE66-45FF-404C-8FE1-225BFA1B609B}" name="Price Mean" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{D93DD236-57DE-4C10-9C84-D6BFBB0CF138}" name="Price Median" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{441B8F93-59E0-44CB-975D-F74259024454}" name="Price SD" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{B596794B-3611-4E3E-8C66-54408D9A271E}" name="Price CV (%)" dataDxfId="48">
       <calculatedColumnFormula>IF(OR(G5&lt;2,H5=0),"",J5/H5*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{921DAC6C-48BB-427A-BCA1-B2F7243D1D39}" name="Price Min" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{62608AB5-9B27-4290-8269-58077B61222B}" name="Price Q1" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{2F9FDB44-93F4-438D-8D00-00ED156DAD26}" name="Price Q3" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{5244D297-7371-414A-A1CC-DFA9E941ABE8}" name="Price Max" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{921DAC6C-48BB-427A-BCA1-B2F7243D1D39}" name="Price Min" dataDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{62608AB5-9B27-4290-8269-58077B61222B}" name="Price Q1" dataDxfId="46"/>
+    <tableColumn id="13" xr3:uid="{2F9FDB44-93F4-438D-8D00-00ED156DAD26}" name="Price Q3" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{5244D297-7371-414A-A1CC-DFA9E941ABE8}" name="Price Max" dataDxfId="44"/>
     <tableColumn id="15" xr3:uid="{3762D7F6-B63A-460C-8353-ED41BCD0B4AA}" name="Rating n"/>
-    <tableColumn id="16" xr3:uid="{DB1AA01E-EA6E-4CB1-B45C-8515EB6EA389}" name="Rating Mean" dataDxfId="40"/>
-    <tableColumn id="17" xr3:uid="{0C4BB8AE-B734-4655-994E-6D3AD5A32FF6}" name="Rating Median" dataDxfId="39"/>
-    <tableColumn id="18" xr3:uid="{723CB2AA-8C24-4054-9C00-5288D705A4F7}" name="Rating SD" dataDxfId="38"/>
-    <tableColumn id="19" xr3:uid="{64A1CFDD-7A08-49D7-88C1-32B0F5C32D77}" name="Rating CV (%)" dataDxfId="37">
+    <tableColumn id="16" xr3:uid="{DB1AA01E-EA6E-4CB1-B45C-8515EB6EA389}" name="Rating Mean" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{0C4BB8AE-B734-4655-994E-6D3AD5A32FF6}" name="Rating Median" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{723CB2AA-8C24-4054-9C00-5288D705A4F7}" name="Rating SD" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{64A1CFDD-7A08-49D7-88C1-32B0F5C32D77}" name="Rating CV (%)" dataDxfId="40">
       <calculatedColumnFormula>IF(OR(P5&lt;2,Q5=0),"",S5/Q5*100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{19D7E071-1F24-4354-8655-D9889530DBA4}" name="Rating Min" dataDxfId="36"/>
-    <tableColumn id="21" xr3:uid="{C5278980-1389-465D-8C80-305B1ADD8D6D}" name="Rating Q1" dataDxfId="35"/>
-    <tableColumn id="22" xr3:uid="{BACFD2F4-8FD5-490E-8D52-8D4B7EA7B9D4}" name="Rating Q3" dataDxfId="34"/>
-    <tableColumn id="23" xr3:uid="{2E494D6A-E1BF-4418-B7A2-2A52C4EDF368}" name="Rating Max" dataDxfId="33"/>
+    <tableColumn id="20" xr3:uid="{19D7E071-1F24-4354-8655-D9889530DBA4}" name="Rating Min" dataDxfId="39"/>
+    <tableColumn id="21" xr3:uid="{C5278980-1389-465D-8C80-305B1ADD8D6D}" name="Rating Q1" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{BACFD2F4-8FD5-490E-8D52-8D4B7EA7B9D4}" name="Rating Q3" dataDxfId="37"/>
+    <tableColumn id="23" xr3:uid="{2E494D6A-E1BF-4418-B7A2-2A52C4EDF368}" name="Rating Max" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1121,105 +3931,105 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{906FAACC-6CC3-4061-9964-52F041EEB448}" name="Table2" displayName="Table2" ref="B2:G117" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{906FAACC-6CC3-4061-9964-52F041EEB448}" name="Table2" displayName="Table2" ref="B2:G117" totalsRowShown="0" headerRowDxfId="35">
   <autoFilter ref="B2:G117" xr:uid="{906FAACC-6CC3-4061-9964-52F041EEB448}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{5F8A3743-7B2E-450F-8C88-897EE84D837A}" name="brand"/>
     <tableColumn id="2" xr3:uid="{E9E857EC-966F-4293-8B8A-5A770CB622B7}" name="model"/>
     <tableColumn id="3" xr3:uid="{7F139F35-B4F0-4FA0-B960-045DAD70040D}" name="platform"/>
     <tableColumn id="4" xr3:uid="{721E18BA-7F9E-45A5-8223-92E98854FFC7}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{1D020644-3DBB-439F-9F33-A85C0882378F}" name="price" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{7468242B-F6C3-45B0-B30A-2CC8AF8E0FB5}" name="rating" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{1D020644-3DBB-439F-9F33-A85C0882378F}" name="price" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{7468242B-F6C3-45B0-B30A-2CC8AF8E0FB5}" name="rating" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D9753A4-423D-4318-A8C3-AB998B29A260}" name="Table3" displayName="Table3" ref="B2:G6" totalsRowShown="0" headerRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D9753A4-423D-4318-A8C3-AB998B29A260}" name="Table3" displayName="Table3" ref="B2:G6" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="B2:G6" xr:uid="{7D9753A4-423D-4318-A8C3-AB998B29A260}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C34BC1F2-B54A-4A22-8C98-E780A12D15DB}" name="brand"/>
     <tableColumn id="2" xr3:uid="{84E4E0EC-897E-4B5F-860C-AB13F8108009}" name="model"/>
     <tableColumn id="3" xr3:uid="{29AA954A-8E7B-478D-A771-15D909E50CA7}" name="platform"/>
     <tableColumn id="4" xr3:uid="{32935E93-46CC-46D5-8863-AD1083E94561}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{4D69F091-E8EF-4DDC-AC79-0008684A07BC}" name="price" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{4FD569B8-3944-4D43-A577-12318CBDEAC2}" name="rating" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{4D69F091-E8EF-4DDC-AC79-0008684A07BC}" name="price" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{4FD569B8-3944-4D43-A577-12318CBDEAC2}" name="rating" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A139ABC-D465-4B40-92B6-8C97957B8ED7}" name="Table4" displayName="Table4" ref="B2:G98" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A139ABC-D465-4B40-92B6-8C97957B8ED7}" name="Table4" displayName="Table4" ref="B2:G98" totalsRowShown="0" headerRowDxfId="29">
   <autoFilter ref="B2:G98" xr:uid="{0A139ABC-D465-4B40-92B6-8C97957B8ED7}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{F238F6B0-2783-4D23-A079-8FAB1E2EB162}" name="brand"/>
     <tableColumn id="2" xr3:uid="{31BD49F0-A64F-4B64-BC15-2002A9BF9944}" name="model"/>
     <tableColumn id="3" xr3:uid="{C664571D-420E-4D1D-ADCC-A015E3ADB438}" name="platform"/>
     <tableColumn id="4" xr3:uid="{D9FB3E6A-2ACA-4AEB-8831-F5C94D7C8A0A}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{863E17D5-A9C0-4BDC-9F07-9E17EA0FD735}" name="price" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{48D10597-7F5D-4CAC-8FD8-C300DAD12618}" name="rating" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{863E17D5-A9C0-4BDC-9F07-9E17EA0FD735}" name="price" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{48D10597-7F5D-4CAC-8FD8-C300DAD12618}" name="rating" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EE051D89-69F4-42DD-B186-74AB34A74FF2}" name="Table5" displayName="Table5" ref="B2:G17" totalsRowShown="0" headerRowDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EE051D89-69F4-42DD-B186-74AB34A74FF2}" name="Table5" displayName="Table5" ref="B2:G17" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="B2:G17" xr:uid="{EE051D89-69F4-42DD-B186-74AB34A74FF2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6377EF2E-C1DF-47E0-B8D4-B1C236445154}" name="brand"/>
     <tableColumn id="2" xr3:uid="{0EAC1C41-D88C-4906-B0FF-492D4DF37727}" name="model"/>
     <tableColumn id="3" xr3:uid="{938BAF50-12CE-4F22-A1E2-4DCA71468076}" name="platform"/>
     <tableColumn id="4" xr3:uid="{5CD7E856-B247-4D29-9B78-4C53F4221A6C}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{1640B708-8860-4D77-ACD6-5DE65B04A3DF}" name="price" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{CC097140-F188-45A3-8526-139F6BEE4C08}" name="rating" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{1640B708-8860-4D77-ACD6-5DE65B04A3DF}" name="price" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{CC097140-F188-45A3-8526-139F6BEE4C08}" name="rating" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2C1BEE2F-536F-4904-BC76-10214916B6E9}" name="Table6" displayName="Table6" ref="B2:G3" totalsRowShown="0" headerRowDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2C1BEE2F-536F-4904-BC76-10214916B6E9}" name="Table6" displayName="Table6" ref="B2:G3" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="B2:G3" xr:uid="{2C1BEE2F-536F-4904-BC76-10214916B6E9}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{47E7C3BE-1277-4151-9943-930751221860}" name="brand"/>
     <tableColumn id="2" xr3:uid="{16CF62A7-45AB-4761-B3D6-FBB953C89456}" name="model"/>
     <tableColumn id="3" xr3:uid="{71205E56-427F-409C-AA48-858ED6DA3893}" name="platform"/>
     <tableColumn id="4" xr3:uid="{69BEFDB9-DB60-4D25-A625-3123F08E7159}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{8C64A8F3-34E9-4549-A9D3-448A40C43A73}" name="price" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{52FD0E9D-0378-4794-9838-54B7BE01E9FE}" name="rating" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{8C64A8F3-34E9-4549-A9D3-448A40C43A73}" name="price" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{52FD0E9D-0378-4794-9838-54B7BE01E9FE}" name="rating" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00DF2E08-75FE-42A6-A78B-7A0356719E91}" name="Table7" displayName="Table7" ref="B2:G28" totalsRowShown="0" headerRowDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00DF2E08-75FE-42A6-A78B-7A0356719E91}" name="Table7" displayName="Table7" ref="B2:G28" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="B2:G28" xr:uid="{00DF2E08-75FE-42A6-A78B-7A0356719E91}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{16864E9E-9C6C-4ADE-9371-CCBD0A603266}" name="brand"/>
     <tableColumn id="2" xr3:uid="{47FAABFD-38B8-4BD2-B6AC-EEBFB844BC2A}" name="model"/>
     <tableColumn id="3" xr3:uid="{C2613F48-F5E2-4737-B86D-3B00728DF669}" name="platform"/>
     <tableColumn id="4" xr3:uid="{16A57B03-E390-4426-A22F-1B6C6D567DC0}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{4DD9B738-E2D7-49DA-9C28-C1016312A6C0}" name="price" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{AE98BD57-7099-42B1-BD96-34598D9C8469}" name="rating" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{4DD9B738-E2D7-49DA-9C28-C1016312A6C0}" name="price" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{AE98BD57-7099-42B1-BD96-34598D9C8469}" name="rating" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39D7B939-1D12-4E20-89C1-D53803C035F2}" name="Table8" displayName="Table8" ref="B2:G8" totalsRowShown="0" headerRowDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39D7B939-1D12-4E20-89C1-D53803C035F2}" name="Table8" displayName="Table8" ref="B2:G8" totalsRowShown="0" headerRowDxfId="17">
   <autoFilter ref="B2:G8" xr:uid="{39D7B939-1D12-4E20-89C1-D53803C035F2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0585998B-A599-4E85-9C6D-D0A5993AD135}" name="brand"/>
     <tableColumn id="2" xr3:uid="{04A956B8-C210-411F-998F-F5C9BB35471A}" name="model"/>
     <tableColumn id="3" xr3:uid="{07C204C7-3E42-421A-A34F-F48F61D4620D}" name="platform"/>
     <tableColumn id="4" xr3:uid="{E99DAA76-FA52-480C-A231-824B5F140354}" name="product_name"/>
-    <tableColumn id="5" xr3:uid="{42E6061D-6621-44D8-85A7-A6CF8AE8F06A}" name="price" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{0562D156-44BF-4498-BB6F-9C9C906DF822}" name="rating" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{42E6061D-6621-44D8-85A7-A6CF8AE8F06A}" name="price" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{0562D156-44BF-4498-BB6F-9C9C906DF822}" name="rating" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1458,58 +4268,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="17.399999999999999">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
     </row>
     <row r="2" spans="2:24" ht="14.4">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
     </row>
     <row r="4" spans="2:24" ht="24.6" customHeight="1">
       <c r="B4" s="3" t="s">
@@ -2416,43 +5226,43 @@
       </c>
     </row>
     <row r="15" spans="2:24">
-      <c r="B15" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="8">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
     </row>
     <row r="16" spans="2:24">
       <c r="B16" t="s">
@@ -2716,45 +5526,45 @@
       </c>
     </row>
     <row r="19" spans="2:24">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="8">
+      <c r="F19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="8">
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
     </row>
     <row r="20" spans="2:24">
       <c r="B20" t="s">
@@ -3647,86 +6457,86 @@
       </c>
     </row>
     <row r="30" spans="2:24">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="8">
+      <c r="F30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="8">
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
     </row>
     <row r="31" spans="2:24">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31" s="8">
+      <c r="F31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="8">
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-      <c r="U31" s="10"/>
-      <c r="V31" s="10"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="10"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
     </row>
     <row r="32" spans="2:24">
       <c r="B32" t="s">
@@ -8023,8 +10833,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
